--- a/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -478,12 +478,12 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.567768" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.282054" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.567768" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18.853482" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20.567768" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.424911" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19.424911" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:7">

--- a/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -480,10 +480,10 @@
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="9.424911" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="19.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.996339" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19.710625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="21.424911" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20.282054" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:7">
